--- a/Load_Test_Report_Finoraax.xlsx
+++ b/Load_Test_Report_Finoraax.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-22 10:14:32</t>
+          <t>2026-07-22 10:16:19</t>
         </is>
       </c>
     </row>
